--- a/customer_satisfaction_evaluation_forms/046_customer_advocacy_assessment_form--customer_satisfaction_evaluation_forms.xlsx
+++ b/customer_satisfaction_evaluation_forms/046_customer_advocacy_assessment_form--customer_satisfaction_evaluation_forms.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -874,7 +874,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>On a scale from 1 to 5</t>
+          <t>Customer Satisfaction Loyalty Score Out Of 5 Scale</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -915,7 +915,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5</t>
+          <t>customer_satisfaction_loyalty_score_out_of_5_2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -943,7 +943,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>On a scale from 1 to 5</t>
+          <t>Customer Awareness About Our Company Scale</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -989,7 +989,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>On a scale from 1 to 5</t>
+          <t>Customer Trust About Our Company Scale</t>
         </is>
       </c>
       <c r="D24" t="inlineStr"/>
@@ -1102,12 +1102,12 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C53"/>
+  <dimension ref="A1:C45"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="10" customWidth="1" min="2" max="2"/>
-    <col width="10" customWidth="1" min="3" max="3"/>
+    <col width="16" customWidth="1" min="2" max="2"/>
+    <col width="16" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1186,12 +1186,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1203,12 +1203,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1356,12 +1356,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1373,12 +1373,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1441,12 +1441,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1458,12 +1458,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1475,12 +1475,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1492,12 +1492,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1509,12 +1509,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1526,12 +1526,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1543,12 +1543,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1560,12 +1560,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1577,12 +1577,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1594,12 +1594,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1611,12 +1611,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
@@ -1628,12 +1628,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1662,352 +1662,216 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>dissatisfied</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Dissatisfied</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_scale_choices</t>
+          <t>customer_satisfaction_loyalty_score_out_of_5_2_choices</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_scale_choices</t>
+          <t>customer_satisfaction_loyalty_score_out_of_5_2_choices</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_choices</t>
+          <t>customer_satisfaction_loyalty_score_out_of_5_2_choices</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_choices</t>
+          <t>customer_awareness_about_our_company_scale_choices</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_choices</t>
+          <t>customer_awareness_about_our_company_scale_choices</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_choices</t>
+          <t>customer_awareness_about_our_company_scale_choices</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>customer_satisfaction_loyalty_score_out_of_5_choices</t>
+          <t>customer_trust_about_our_company_scale_choices</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Option 5</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>customer_awareness_about_our_company_scale_choices</t>
+          <t>customer_trust_about_our_company_scale_choices</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>option_1</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Option 1</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>customer_awareness_about_our_company_scale_choices</t>
+          <t>customer_trust_about_our_company_scale_choices</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>option_2</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Option 2</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>customer_awareness_about_our_company_scale_choices</t>
+          <t>customer_loyalty_program_participation_choices</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>option_3</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Option 3</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>customer_awareness_about_our_company_scale_choices</t>
+          <t>customer_loyalty_program_participation_choices</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>option_4</t>
+          <t>no</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Option 4</t>
+          <t>No</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>customer_awareness_about_our_company_scale_choices</t>
+          <t>customer_loyalty_program_participation_choices</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>option_5</t>
+          <t>other</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" t="inlineStr">
-        <is>
-          <t>customer_trust_about_our_company_scale_choices</t>
-        </is>
-      </c>
-      <c r="B46" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C46" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t>customer_trust_about_our_company_scale_choices</t>
-        </is>
-      </c>
-      <c r="B47" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C47" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" t="inlineStr">
-        <is>
-          <t>customer_trust_about_our_company_scale_choices</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C48" t="inlineStr">
-        <is>
-          <t>Option 3</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" t="inlineStr">
-        <is>
-          <t>customer_trust_about_our_company_scale_choices</t>
-        </is>
-      </c>
-      <c r="B49" t="inlineStr">
-        <is>
-          <t>option_4</t>
-        </is>
-      </c>
-      <c r="C49" t="inlineStr">
-        <is>
-          <t>Option 4</t>
-        </is>
-      </c>
-    </row>
-    <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>customer_trust_about_our_company_scale_choices</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>option_5</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>Option 5</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>customer_loyalty_program_participation_choices</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>option_1</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>Option 1</t>
-        </is>
-      </c>
-    </row>
-    <row r="52">
-      <c r="A52" t="inlineStr">
-        <is>
-          <t>customer_loyalty_program_participation_choices</t>
-        </is>
-      </c>
-      <c r="B52" t="inlineStr">
-        <is>
-          <t>option_2</t>
-        </is>
-      </c>
-      <c r="C52" t="inlineStr">
-        <is>
-          <t>Option 2</t>
-        </is>
-      </c>
-    </row>
-    <row r="53">
-      <c r="A53" t="inlineStr">
-        <is>
-          <t>customer_loyalty_program_participation_choices</t>
-        </is>
-      </c>
-      <c r="B53" t="inlineStr">
-        <is>
-          <t>option_3</t>
-        </is>
-      </c>
-      <c r="C53" t="inlineStr">
-        <is>
-          <t>Option 3</t>
+          <t>Other</t>
         </is>
       </c>
     </row>
